--- a/合同全生命周期管理系统-项目管理套件/06_风险问题与变更/风险管理-20260918-V1.xlsx
+++ b/合同全生命周期管理系统-项目管理套件/06_风险问题与变更/风险管理-20260918-V1.xlsx
@@ -9790,18 +9790,23 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="B10" s="30">
+        <x:f>COUNTIFS(风险登记册!$L$9:$L$1000,$A10,风险登记册!$T$9:$T$1000,B$9)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="C10" s="31">
+        <x:f>COUNTIFS(风险登记册!$L$9:$L$1000,$A10,风险登记册!$T$9:$T$1000,C$9)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="D10" s="31">
+        <x:f>COUNTIFS(风险登记册!$L$9:$L$1000,$A10,风险登记册!$T$9:$T$1000,D$9)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="E10" s="32">
-        <x:v>3</x:v>
+        <x:f>COUNTIFS(风险登记册!$L$9:$L$1000,$A10,风险登记册!$T$9:$T$1000,E$9)</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F10" s="32">
+        <x:f>COUNTIFS(风险登记册!$L$9:$L$1000,$A10,风险登记册!$T$9:$T$1000,F$9)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="G10" s="24"/>
@@ -9810,18 +9815,23 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="J10" s="30">
+        <x:f>COUNTIFS(风险登记册!$AE$9:$AE$1000,$I10,风险登记册!$AF$9:$AF$1000,J$9)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="K10" s="31">
+        <x:f>COUNTIFS(风险登记册!$AE$9:$AE$1000,$I10,风险登记册!$AF$9:$AF$1000,K$9)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="L10" s="31">
-        <x:v>1</x:v>
+        <x:f>COUNTIFS(风险登记册!$AE$9:$AE$1000,$I10,风险登记册!$AF$9:$AF$1000,L$9)</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="M10" s="32">
+        <x:f>COUNTIFS(风险登记册!$AE$9:$AE$1000,$I10,风险登记册!$AF$9:$AF$1000,M$9)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="N10" s="32">
+        <x:f>COUNTIFS(风险登记册!$AE$9:$AE$1000,$I10,风险登记册!$AF$9:$AF$1000,N$9)</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
@@ -9830,19 +9840,24 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="B11" s="33">
+        <x:f>COUNTIFS(风险登记册!$L$9:$L$1000,$A11,风险登记册!$T$9:$T$1000,B$9)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="C11" s="30">
+        <x:f>COUNTIFS(风险登记册!$L$9:$L$1000,$A11,风险登记册!$T$9:$T$1000,C$9)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="D11" s="31">
-        <x:v>5</x:v>
+        <x:f>COUNTIFS(风险登记册!$L$9:$L$1000,$A11,风险登记册!$T$9:$T$1000,D$9)</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E11" s="31">
+        <x:f>COUNTIFS(风险登记册!$L$9:$L$1000,$A11,风险登记册!$T$9:$T$1000,E$9)</x:f>
         <x:v>4</x:v>
       </x:c>
       <x:c r="F11" s="32">
-        <x:v>0</x:v>
+        <x:f>COUNTIFS(风险登记册!$L$9:$L$1000,$A11,风险登记册!$T$9:$T$1000,F$9)</x:f>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="G11" s="24"/>
       <x:c r="H11" s="24"/>
@@ -9850,18 +9865,23 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="J11" s="33">
+        <x:f>COUNTIFS(风险登记册!$AE$9:$AE$1000,$I11,风险登记册!$AF$9:$AF$1000,J$9)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="K11" s="30">
-        <x:v>3</x:v>
+        <x:f>COUNTIFS(风险登记册!$AE$9:$AE$1000,$I11,风险登记册!$AF$9:$AF$1000,K$9)</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="L11" s="31">
-        <x:v>7</x:v>
+        <x:f>COUNTIFS(风险登记册!$AE$9:$AE$1000,$I11,风险登记册!$AF$9:$AF$1000,L$9)</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="M11" s="31">
+        <x:f>COUNTIFS(风险登记册!$AE$9:$AE$1000,$I11,风险登记册!$AF$9:$AF$1000,M$9)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="N11" s="32">
+        <x:f>COUNTIFS(风险登记册!$AE$9:$AE$1000,$I11,风险登记册!$AF$9:$AF$1000,N$9)</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
@@ -9870,18 +9890,23 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B12" s="33">
+        <x:f>COUNTIFS(风险登记册!$L$9:$L$1000,$A12,风险登记册!$T$9:$T$1000,B$9)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="C12" s="30">
+        <x:f>COUNTIFS(风险登记册!$L$9:$L$1000,$A12,风险登记册!$T$9:$T$1000,C$9)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="D12" s="30">
+        <x:f>COUNTIFS(风险登记册!$L$9:$L$1000,$A12,风险登记册!$T$9:$T$1000,D$9)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="E12" s="31">
-        <x:v>0</x:v>
+        <x:f>COUNTIFS(风险登记册!$L$9:$L$1000,$A12,风险登记册!$T$9:$T$1000,E$9)</x:f>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="F12" s="31">
+        <x:f>COUNTIFS(风险登记册!$L$9:$L$1000,$A12,风险登记册!$T$9:$T$1000,F$9)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="G12" s="24"/>
@@ -9890,19 +9915,24 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="J12" s="33">
+        <x:f>COUNTIFS(风险登记册!$AE$9:$AE$1000,$I12,风险登记册!$AF$9:$AF$1000,J$9)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="K12" s="30">
+        <x:f>COUNTIFS(风险登记册!$AE$9:$AE$1000,$I12,风险登记册!$AF$9:$AF$1000,K$9)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="L12" s="30">
+        <x:f>COUNTIFS(风险登记册!$AE$9:$AE$1000,$I12,风险登记册!$AF$9:$AF$1000,L$9)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="M12" s="31">
-        <x:v>0</x:v>
+        <x:f>COUNTIFS(风险登记册!$AE$9:$AE$1000,$I12,风险登记册!$AF$9:$AF$1000,M$9)</x:f>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="N12" s="31">
-        <x:v>0</x:v>
+        <x:f>COUNTIFS(风险登记册!$AE$9:$AE$1000,$I12,风险登记册!$AF$9:$AF$1000,N$9)</x:f>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:14">
@@ -9910,18 +9940,23 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B13" s="33">
+        <x:f>COUNTIFS(风险登记册!$L$9:$L$1000,$A13,风险登记册!$T$9:$T$1000,B$9)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="C13" s="33">
+        <x:f>COUNTIFS(风险登记册!$L$9:$L$1000,$A13,风险登记册!$T$9:$T$1000,C$9)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="D13" s="30">
+        <x:f>COUNTIFS(风险登记册!$L$9:$L$1000,$A13,风险登记册!$T$9:$T$1000,D$9)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="E13" s="30">
+        <x:f>COUNTIFS(风险登记册!$L$9:$L$1000,$A13,风险登记册!$T$9:$T$1000,E$9)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="F13" s="31">
+        <x:f>COUNTIFS(风险登记册!$L$9:$L$1000,$A13,风险登记册!$T$9:$T$1000,F$9)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="G13" s="24"/>
@@ -9930,18 +9965,23 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="J13" s="33">
+        <x:f>COUNTIFS(风险登记册!$AE$9:$AE$1000,$I13,风险登记册!$AF$9:$AF$1000,J$9)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="K13" s="33">
+        <x:f>COUNTIFS(风险登记册!$AE$9:$AE$1000,$I13,风险登记册!$AF$9:$AF$1000,K$9)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="L13" s="30">
+        <x:f>COUNTIFS(风险登记册!$AE$9:$AE$1000,$I13,风险登记册!$AF$9:$AF$1000,L$9)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="M13" s="30">
-        <x:v>0</x:v>
+        <x:f>COUNTIFS(风险登记册!$AE$9:$AE$1000,$I13,风险登记册!$AF$9:$AF$1000,M$9)</x:f>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="N13" s="31">
+        <x:f>COUNTIFS(风险登记册!$AE$9:$AE$1000,$I13,风险登记册!$AF$9:$AF$1000,N$9)</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
@@ -9950,18 +9990,23 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="B14" s="33">
+        <x:f>COUNTIFS(风险登记册!$L$9:$L$1000,$A14,风险登记册!$T$9:$T$1000,B$9)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="C14" s="33">
+        <x:f>COUNTIFS(风险登记册!$L$9:$L$1000,$A14,风险登记册!$T$9:$T$1000,C$9)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="D14" s="33">
+        <x:f>COUNTIFS(风险登记册!$L$9:$L$1000,$A14,风险登记册!$T$9:$T$1000,D$9)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="E14" s="33">
+        <x:f>COUNTIFS(风险登记册!$L$9:$L$1000,$A14,风险登记册!$T$9:$T$1000,E$9)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="F14" s="30">
+        <x:f>COUNTIFS(风险登记册!$L$9:$L$1000,$A14,风险登记册!$T$9:$T$1000,F$9)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="G14" s="24"/>
@@ -9970,18 +10015,23 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="J14" s="33">
+        <x:f>COUNTIFS(风险登记册!$AE$9:$AE$1000,$I14,风险登记册!$AF$9:$AF$1000,J$9)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="K14" s="33">
+        <x:f>COUNTIFS(风险登记册!$AE$9:$AE$1000,$I14,风险登记册!$AF$9:$AF$1000,K$9)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="L14" s="33">
+        <x:f>COUNTIFS(风险登记册!$AE$9:$AE$1000,$I14,风险登记册!$AF$9:$AF$1000,L$9)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="M14" s="33">
+        <x:f>COUNTIFS(风险登记册!$AE$9:$AE$1000,$I14,风险登记册!$AF$9:$AF$1000,M$9)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="N14" s="30">
+        <x:f>COUNTIFS(风险登记册!$AE$9:$AE$1000,$I14,风险登记册!$AF$9:$AF$1000,N$9)</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>

--- a/合同全生命周期管理系统-项目管理套件/06_风险问题与变更/风险管理-20260918-V1.xlsx
+++ b/合同全生命周期管理系统-项目管理套件/06_风险问题与变更/风险管理-20260918-V1.xlsx
@@ -7,6 +7,7 @@
     <x:workbookView windowWidth="28260" windowHeight="12660"/>
   </x:bookViews>
   <x:sheets>
+    <x:sheet name="使用说明" sheetId="11" r:id="rId8"/>
     <x:sheet name="风险管理计划" sheetId="1" r:id="rId1"/>
     <x:sheet name="风险登记册" sheetId="2" r:id="rId2"/>
     <x:sheet name="风险热力图" sheetId="3" r:id="rId3"/>
@@ -14,7 +15,6 @@
     <x:sheet name="重大风险应对" sheetId="5" r:id="rId5"/>
     <x:sheet name="风险应对计划" sheetId="6" r:id="rId6"/>
     <x:sheet name="_数据接口" sheetId="10" r:id="rId7"/>
-    <x:sheet name="使用说明" sheetId="11" r:id="rId8"/>
   </x:sheets>
   <x:calcPr calcId="191029" fullCalcOnLoad="1"/>
   <x:extLst>
